--- a/Exc1/Проблемы.xlsx
+++ b/Exc1/Проблемы.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="30">
   <si>
     <t>Проблемное место</t>
   </si>
@@ -77,13 +77,37 @@
   </si>
   <si>
     <t xml:space="preserve"> UX можно улучшить в последний момент, но забывать про это нельзя</t>
+  </si>
+  <si>
+    <t>* Минусы из за которых хочется отказаться от Apache Camel</t>
+  </si>
+  <si>
+    <t>Ограниченная масштабируемость. Framework не предназначен для обработки больших объёмов данных.</t>
+  </si>
+  <si>
+    <t>Отсутствие поддержки длительного хранения. Для этого требуется дополнительный кэш или хранилище.</t>
+  </si>
+  <si>
+    <t>Отсутствие серверного облака. Framework предназначен для использования в одном дата-центре или облачном регионе, но не в гибридных или мультиоблачных сценариях.</t>
+  </si>
+  <si>
+    <t>Сложности с тестированием. Нелегко проводить тесты с реальными маршрутами, для этого нужно писать специальные тестовые маршруты.</t>
+  </si>
+  <si>
+    <t>Чрезмерное использование ресурсов. Это происходит при обработке больших объёмов данных или при интеграции с системами, которые требуют много процессорной мощности или памяти.</t>
+  </si>
+  <si>
+    <t>Сложная настройка и документация. Например, могут возникать проблемы с конфигурацией и пониманием документации.</t>
+  </si>
+  <si>
+    <t>P.S. C замечанием согласен, добавил аргументацию)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -92,6 +116,11 @@
     </font>
     <font>
       <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <color rgb="FFFF0000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
@@ -124,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -133,6 +162,13 @@
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,6 +484,67 @@
         <v>21</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:Z1">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
